--- a/reports/sales_report.xlsx
+++ b/reports/sales_report.xlsx
@@ -818,11 +818,11 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
